--- a/output/daily_ratings/ratings_2026-03-17.xlsx
+++ b/output/daily_ratings/ratings_2026-03-17.xlsx
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>90.51900691870576</v>
+        <v>96.02182356505553</v>
       </c>
       <c r="T2" t="n">
-        <v>90.51900691870576</v>
+        <v>96.02182356505553</v>
       </c>
     </row>
     <row r="3">
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>96.50101599635946</v>
+        <v>97.88555511880749</v>
       </c>
       <c r="T3" t="n">
-        <v>96.50101599635946</v>
+        <v>97.88555511880749</v>
       </c>
     </row>
     <row r="4">
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>95.36944916102962</v>
+        <v>96.75398828347765</v>
       </c>
       <c r="T4" t="n">
-        <v>95.36944916102962</v>
+        <v>96.75398828347765</v>
       </c>
     </row>
     <row r="5">
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>92.6189390070556</v>
+        <v>94.00347812950363</v>
       </c>
       <c r="T5" t="n">
-        <v>92.6189390070556</v>
+        <v>94.00347812950363</v>
       </c>
     </row>
     <row r="6">
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>87.96099832988365</v>
+        <v>85.59513379888043</v>
       </c>
       <c r="T6" t="n">
-        <v>87.96099832988365</v>
+        <v>85.59513379888043</v>
       </c>
     </row>
     <row r="7">
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>92.26161230020737</v>
+        <v>89.89574776920415</v>
       </c>
       <c r="T7" t="n">
-        <v>92.26161230020737</v>
+        <v>89.89574776920415</v>
       </c>
     </row>
     <row r="8">
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>88.74506767338929</v>
+        <v>86.37920314238606</v>
       </c>
       <c r="T8" t="n">
-        <v>88.74506767338929</v>
+        <v>86.37920314238606</v>
       </c>
     </row>
     <row r="9">
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>86.26313065951624</v>
+        <v>77.81404494306176</v>
       </c>
       <c r="T9" t="n">
-        <v>86.26313065951624</v>
+        <v>77.81404494306176</v>
       </c>
     </row>
     <row r="10">
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>88.71804794674955</v>
+        <v>80.26896223029507</v>
       </c>
       <c r="T10" t="n">
-        <v>88.71804794674955</v>
+        <v>80.26896223029507</v>
       </c>
     </row>
     <row r="11">
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>86.82044663857566</v>
+        <v>78.37136092212118</v>
       </c>
       <c r="T11" t="n">
-        <v>86.82044663857566</v>
+        <v>78.37136092212118</v>
       </c>
     </row>
     <row r="12">
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>81.80790280739257</v>
+        <v>73.35881709093809</v>
       </c>
       <c r="T12" t="n">
-        <v>81.80790280739257</v>
+        <v>73.35881709093809</v>
       </c>
     </row>
     <row r="13">
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>84.26282009462591</v>
+        <v>75.81373437817143</v>
       </c>
       <c r="T13" t="n">
-        <v>84.26282009462591</v>
+        <v>75.81373437817143</v>
       </c>
     </row>
     <row r="14">
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>82.09970841856787</v>
+        <v>64.67291476423577</v>
       </c>
       <c r="T14" t="n">
-        <v>82.09970841856787</v>
+        <v>64.67291476423577</v>
       </c>
     </row>
     <row r="15">
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>79.05360539785315</v>
+        <v>61.62681174352104</v>
       </c>
       <c r="T15" t="n">
-        <v>79.05360539785315</v>
+        <v>61.62681174352104</v>
       </c>
     </row>
     <row r="16">
@@ -1696,10 +1696,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S17" t="n">
-        <v>76.48077438597036</v>
+        <v>81.98359103232013</v>
       </c>
       <c r="T17" t="n">
-        <v>76.48077438597036</v>
+        <v>81.98359103232013</v>
       </c>
     </row>
     <row r="18">
@@ -1770,10 +1770,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S18" t="n">
-        <v>79.38998705401717</v>
+        <v>83.91616208836658</v>
       </c>
       <c r="T18" t="n">
-        <v>79.38998705401717</v>
+        <v>83.91616208836658</v>
       </c>
     </row>
     <row r="19">
@@ -1844,10 +1844,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S19" t="n">
-        <v>75.43797056896824</v>
+        <v>79.96414560331765</v>
       </c>
       <c r="T19" t="n">
-        <v>75.43797056896824</v>
+        <v>79.96414560331765</v>
       </c>
     </row>
     <row r="20">
@@ -1918,10 +1918,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S20" t="n">
-        <v>74.76746898731083</v>
+        <v>76.15200810975887</v>
       </c>
       <c r="T20" t="n">
-        <v>74.76746898731083</v>
+        <v>76.15200810975887</v>
       </c>
     </row>
     <row r="21">
@@ -1992,10 +1992,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S21" t="n">
-        <v>76.31757280366054</v>
+        <v>77.70211192610857</v>
       </c>
       <c r="T21" t="n">
-        <v>76.31757280366054</v>
+        <v>77.70211192610857</v>
       </c>
     </row>
     <row r="22">
@@ -2066,10 +2066,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S22" t="n">
-        <v>66.75962676704593</v>
+        <v>68.14416588949396</v>
       </c>
       <c r="T22" t="n">
-        <v>66.75962676704593</v>
+        <v>68.14416588949396</v>
       </c>
     </row>
     <row r="23">
@@ -2140,10 +2140,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S23" t="n">
-        <v>68.68236860806837</v>
+        <v>66.31650407706515</v>
       </c>
       <c r="T23" t="n">
-        <v>68.68236860806837</v>
+        <v>66.31650407706515</v>
       </c>
     </row>
     <row r="24">
@@ -2216,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>81.16998132357696</v>
+        <v>86.67279796992673</v>
       </c>
       <c r="T24" t="n">
-        <v>81.16998132357696</v>
+        <v>86.67279796992673</v>
       </c>
     </row>
     <row r="25">
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>82.3811139691219</v>
+        <v>83.76565309156993</v>
       </c>
       <c r="T25" t="n">
-        <v>82.3811139691219</v>
+        <v>83.76565309156993</v>
       </c>
     </row>
     <row r="26">
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>79.88920089203258</v>
+        <v>81.27374001448061</v>
       </c>
       <c r="T26" t="n">
-        <v>79.88920089203258</v>
+        <v>81.27374001448061</v>
       </c>
     </row>
     <row r="27">
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>78.79436308155584</v>
+        <v>76.42849855055262</v>
       </c>
       <c r="T27" t="n">
-        <v>78.79436308155584</v>
+        <v>76.42849855055262</v>
       </c>
     </row>
     <row r="28">
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>80.89865684153092</v>
+        <v>78.5327923105277</v>
       </c>
       <c r="T28" t="n">
-        <v>80.89865684153092</v>
+        <v>78.5327923105277</v>
       </c>
     </row>
     <row r="29">
@@ -2586,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>80.52607111085631</v>
+        <v>72.07698539440183</v>
       </c>
       <c r="T29" t="n">
-        <v>80.52607111085631</v>
+        <v>72.07698539440183</v>
       </c>
     </row>
     <row r="30">
@@ -2660,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>78.86948485173639</v>
+        <v>70.42039913528191</v>
       </c>
       <c r="T30" t="n">
-        <v>78.86948485173639</v>
+        <v>70.42039913528191</v>
       </c>
     </row>
     <row r="31">
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>77.29139509912619</v>
+        <v>68.84230938267171</v>
       </c>
       <c r="T31" t="n">
-        <v>77.29139509912619</v>
+        <v>68.84230938267171</v>
       </c>
     </row>
     <row r="32">
@@ -2808,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>75.24956498340121</v>
+        <v>57.82277132906911</v>
       </c>
       <c r="T32" t="n">
-        <v>75.24956498340121</v>
+        <v>57.82277132906911</v>
       </c>
     </row>
     <row r="33">
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>49.98008172526779</v>
+        <v>55.48289837161757</v>
       </c>
       <c r="T33" t="n">
-        <v>49.98008172526779</v>
+        <v>55.48289837161757</v>
       </c>
     </row>
     <row r="34">
@@ -2958,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>50.62621942201206</v>
+        <v>52.0107585444601</v>
       </c>
       <c r="T34" t="n">
-        <v>50.62621942201206</v>
+        <v>52.0107585444601</v>
       </c>
     </row>
     <row r="35">
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>49.97952912818896</v>
+        <v>51.364068250637</v>
       </c>
       <c r="T35" t="n">
-        <v>49.97952912818896</v>
+        <v>51.364068250637</v>
       </c>
     </row>
     <row r="36">
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>49.0094936874543</v>
+        <v>50.39403280990233</v>
       </c>
       <c r="T36" t="n">
-        <v>49.0094936874543</v>
+        <v>50.39403280990233</v>
       </c>
     </row>
     <row r="37">
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>49.64619010153375</v>
+        <v>51.03072922398179</v>
       </c>
       <c r="T37" t="n">
-        <v>49.64619010153375</v>
+        <v>51.03072922398179</v>
       </c>
     </row>
     <row r="38">
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>53.19259278709443</v>
+        <v>50.8267282560912</v>
       </c>
       <c r="T38" t="n">
-        <v>53.19259278709443</v>
+        <v>50.8267282560912</v>
       </c>
     </row>
     <row r="39">
@@ -3328,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>50.69048840067163</v>
+        <v>48.3246238696684</v>
       </c>
       <c r="T39" t="n">
-        <v>50.69048840067163</v>
+        <v>48.3246238696684</v>
       </c>
     </row>
     <row r="40">
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>50.80983257969258</v>
+        <v>48.44396804868936</v>
       </c>
       <c r="T40" t="n">
-        <v>50.80983257969258</v>
+        <v>48.44396804868936</v>
       </c>
     </row>
     <row r="41">
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>55.40437282283079</v>
+        <v>37.97757916849869</v>
       </c>
       <c r="T41" t="n">
-        <v>55.40437282283079</v>
+        <v>37.97757916849869</v>
       </c>
     </row>
     <row r="42">
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>98.71890959833847</v>
+        <v>104.2217262446882</v>
       </c>
       <c r="T42" t="n">
-        <v>98.71890959833847</v>
+        <v>104.2217262446882</v>
       </c>
     </row>
     <row r="43">
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>100.229561776282</v>
+        <v>104.7557368106314</v>
       </c>
       <c r="T43" t="n">
-        <v>100.229561776282</v>
+        <v>104.7557368106314</v>
       </c>
     </row>
     <row r="44">
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>100.0748791716814</v>
+        <v>104.6010542060308</v>
       </c>
       <c r="T44" t="n">
-        <v>100.0748791716814</v>
+        <v>104.6010542060308</v>
       </c>
     </row>
     <row r="45">
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>100.1228629915706</v>
+        <v>101.5074021140186</v>
       </c>
       <c r="T45" t="n">
-        <v>100.1228629915706</v>
+        <v>101.5074021140186</v>
       </c>
     </row>
     <row r="46">
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>99.73615648006906</v>
+        <v>101.1206956025171</v>
       </c>
       <c r="T46" t="n">
-        <v>99.73615648006906</v>
+        <v>101.1206956025171</v>
       </c>
     </row>
     <row r="47">
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>106.5359409245786</v>
+        <v>104.1700763935754</v>
       </c>
       <c r="T47" t="n">
-        <v>106.5359409245786</v>
+        <v>104.1700763935754</v>
       </c>
     </row>
     <row r="48">
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>100.7796145530096</v>
+        <v>98.4137500220064</v>
       </c>
       <c r="T48" t="n">
-        <v>100.7796145530096</v>
+        <v>98.4137500220064</v>
       </c>
     </row>
     <row r="49">
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>99.96717529878538</v>
+        <v>97.60131076778215</v>
       </c>
       <c r="T49" t="n">
-        <v>99.96717529878538</v>
+        <v>97.60131076778215</v>
       </c>
     </row>
     <row r="50">
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>104.4961918880716</v>
+        <v>96.04710617161709</v>
       </c>
       <c r="T50" t="n">
-        <v>104.4961918880716</v>
+        <v>96.04710617161709</v>
       </c>
     </row>
     <row r="51">
@@ -4218,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>101.3877826957414</v>
+        <v>92.93869697928695</v>
       </c>
       <c r="T51" t="n">
-        <v>101.3877826957414</v>
+        <v>92.93869697928695</v>
       </c>
     </row>
     <row r="52">
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>108.0304944642919</v>
+        <v>90.60370080995983</v>
       </c>
       <c r="T52" t="n">
-        <v>108.0304944642919</v>
+        <v>90.60370080995983</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_ratings/ratings_2026-03-17.xlsx
+++ b/output/daily_ratings/ratings_2026-03-17.xlsx
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P2" t="n">
-        <v>129.3747839743286</v>
+        <v>122.6866853493338</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.438970000000012</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>96.02182356505553</v>
+        <v>92.30837681340935</v>
       </c>
       <c r="T2" t="n">
-        <v>96.02182356505553</v>
+        <v>92.30837681340935</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +650,10 @@
         <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P3" t="n">
-        <v>123.23818057629</v>
+        <v>116.5620214842595</v>
       </c>
       <c r="Q3" t="n">
         <v>7.379509999999982</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>97.88555511880749</v>
+        <v>94.16630760610863</v>
       </c>
       <c r="T3" t="n">
-        <v>97.88555511880749</v>
+        <v>94.16630760610863</v>
       </c>
     </row>
     <row r="4">
@@ -724,10 +724,10 @@
         <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P4" t="n">
-        <v>122.7121859993152</v>
+        <v>116.0370502958245</v>
       </c>
       <c r="Q4" t="n">
         <v>6.277199999999993</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>96.75398828347765</v>
+        <v>93.04396826409675</v>
       </c>
       <c r="T4" t="n">
-        <v>96.75398828347765</v>
+        <v>93.04396826409675</v>
       </c>
     </row>
     <row r="5">
@@ -798,10 +798,10 @@
         <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P5" t="n">
-        <v>120.9588707427328</v>
+        <v>114.2871463343747</v>
       </c>
       <c r="Q5" t="n">
         <v>4.072579999999988</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>94.00347812950363</v>
+        <v>90.31652456696133</v>
       </c>
       <c r="T5" t="n">
-        <v>94.00347812950363</v>
+        <v>90.31652456696133</v>
       </c>
     </row>
     <row r="6">
@@ -872,10 +872,10 @@
         <v>3.65</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P6" t="n">
-        <v>116.5755826012766</v>
+        <v>109.9123864307502</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>85.59513379888043</v>
+        <v>81.97738415976636</v>
       </c>
       <c r="T6" t="n">
-        <v>85.59513379888043</v>
+        <v>81.97738415976636</v>
       </c>
     </row>
     <row r="7">
@@ -946,10 +946,10 @@
         <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P7" t="n">
-        <v>113.9456097164029</v>
+        <v>107.2875304885755</v>
       </c>
       <c r="Q7" t="n">
         <v>5.174889999999976</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>89.89574776920415</v>
+        <v>86.24914001802358</v>
       </c>
       <c r="T7" t="n">
-        <v>89.89574776920415</v>
+        <v>86.24914001802358</v>
       </c>
     </row>
     <row r="8">
@@ -1020,10 +1020,10 @@
         <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P8" t="n">
-        <v>112.1922944598204</v>
+        <v>105.5376265271257</v>
       </c>
       <c r="Q8" t="n">
         <v>1.867959999999982</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>86.37920314238606</v>
+        <v>82.76143073870998</v>
       </c>
       <c r="T8" t="n">
-        <v>86.37920314238606</v>
+        <v>82.76143073870998</v>
       </c>
     </row>
     <row r="9">
@@ -1094,10 +1094,10 @@
         <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P9" t="n">
-        <v>108.6856639466555</v>
+        <v>102.0378186042261</v>
       </c>
       <c r="Q9" t="n">
         <v>-6.950520000000012</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>77.81404494306176</v>
+        <v>74.26548101572627</v>
       </c>
       <c r="T9" t="n">
-        <v>77.81404494306176</v>
+        <v>74.26548101572627</v>
       </c>
     </row>
     <row r="10">
@@ -1168,10 +1168,10 @@
         <v>6.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P10" t="n">
-        <v>107.8090063183643</v>
+        <v>101.1628666235012</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.541280000000015</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>80.26896223029507</v>
+        <v>76.70308707804963</v>
       </c>
       <c r="T10" t="n">
-        <v>80.26896223029507</v>
+        <v>76.70308707804963</v>
       </c>
     </row>
     <row r="11">
@@ -1242,10 +1242,10 @@
         <v>6.300000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P11" t="n">
-        <v>107.2830117413895</v>
+        <v>100.6378954350663</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.745900000000006</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>78.37136092212118</v>
+        <v>74.82048215385953</v>
       </c>
       <c r="T11" t="n">
-        <v>78.37136092212118</v>
+        <v>74.82048215385953</v>
       </c>
     </row>
     <row r="12">
@@ -1316,10 +1316,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P12" t="n">
-        <v>96.76312020189472</v>
+        <v>90.13847166636748</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.438970000000012</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>73.35881709093809</v>
+        <v>69.85980370372027</v>
       </c>
       <c r="T12" t="n">
-        <v>73.35881709093809</v>
+        <v>69.85980370372027</v>
       </c>
     </row>
     <row r="13">
@@ -1390,10 +1390,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P13" t="n">
-        <v>95.8864625736035</v>
+        <v>89.26351968564259</v>
       </c>
       <c r="Q13" t="n">
         <v>2.970269999999999</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>75.81373437817143</v>
+        <v>72.29740976604367</v>
       </c>
       <c r="T13" t="n">
-        <v>75.81373437817143</v>
+        <v>72.29740976604367</v>
       </c>
     </row>
     <row r="14">
@@ -1464,10 +1464,10 @@
         <v>12.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P14" t="n">
-        <v>85.36657103410869</v>
+        <v>78.76409591694377</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.541280000000015</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>64.67291476423577</v>
+        <v>61.25460665847866</v>
       </c>
       <c r="T14" t="n">
-        <v>64.67291476423577</v>
+        <v>61.25460665847866</v>
       </c>
     </row>
     <row r="15">
@@ -1538,10 +1538,10 @@
         <v>13.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P15" t="n">
-        <v>80.98328289265251</v>
+        <v>74.38933601331928</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>61.62681174352104</v>
+        <v>58.23732532653122</v>
       </c>
       <c r="T15" t="n">
-        <v>61.62681174352104</v>
+        <v>58.23732532653122</v>
       </c>
     </row>
     <row r="16">
@@ -1612,10 +1612,10 @@
         <v>20.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P16" t="n">
-        <v>61.49968011053053</v>
+        <v>53.66937268787446</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.643590000000017</v>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P17" t="n">
-        <v>102.8997235999335</v>
+        <v>96.26313553144195</v>
       </c>
       <c r="Q17" t="n">
         <v>0.7656499999999937</v>
@@ -1696,10 +1696,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S17" t="n">
-        <v>81.98359103232013</v>
+        <v>78.41139104514895</v>
       </c>
       <c r="T17" t="n">
-        <v>81.98359103232013</v>
+        <v>78.41139104514895</v>
       </c>
     </row>
     <row r="18">
@@ -1758,10 +1758,10 @@
         <v>0.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P18" t="n">
-        <v>102.3737290229588</v>
+        <v>95.738164343007</v>
       </c>
       <c r="Q18" t="n">
         <v>4.072579999999988</v>
@@ -1770,10 +1770,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S18" t="n">
-        <v>83.91616208836658</v>
+        <v>80.33011403184989</v>
       </c>
       <c r="T18" t="n">
-        <v>83.91616208836658</v>
+        <v>80.33011403184989</v>
       </c>
     </row>
     <row r="19">
@@ -1832,10 +1832,10 @@
         <v>0.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P19" t="n">
-        <v>102.1983974973005</v>
+        <v>95.56317394686202</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.438970000000012</v>
@@ -1844,10 +1844,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S19" t="n">
-        <v>79.96414560331765</v>
+        <v>76.40809486768089</v>
       </c>
       <c r="T19" t="n">
-        <v>79.96414560331765</v>
+        <v>76.40809486768089</v>
       </c>
     </row>
     <row r="20">
@@ -1906,10 +1906,10 @@
         <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P20" t="n">
-        <v>97.81510935584437</v>
+        <v>91.18841404323753</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.541280000000015</v>
@@ -1918,10 +1918,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S20" t="n">
-        <v>76.15200810975887</v>
+        <v>72.63054795355524</v>
       </c>
       <c r="T20" t="n">
-        <v>76.15200810975887</v>
+        <v>72.63054795355524</v>
       </c>
     </row>
     <row r="21">
@@ -1980,10 +1980,10 @@
         <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P21" t="n">
-        <v>93.43182121438821</v>
+        <v>86.81365413961302</v>
       </c>
       <c r="Q21" t="n">
         <v>4.072579999999988</v>
@@ -1992,10 +1992,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S21" t="n">
-        <v>77.70211192610857</v>
+        <v>74.17486011467707</v>
       </c>
       <c r="T21" t="n">
-        <v>77.70211192610857</v>
+        <v>74.17486011467707</v>
       </c>
     </row>
     <row r="22">
@@ -2054,10 +2054,10 @@
         <v>2.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P22" t="n">
-        <v>92.90582663741345</v>
+        <v>86.28868295117807</v>
       </c>
       <c r="Q22" t="n">
         <v>-9.155140000000017</v>
@@ -2066,10 +2066,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S22" t="n">
-        <v>68.14416588949396</v>
+        <v>64.68959936870476</v>
       </c>
       <c r="T22" t="n">
-        <v>68.14416588949396</v>
+        <v>64.68959936870476</v>
       </c>
     </row>
     <row r="23">
@@ -2128,10 +2128,10 @@
         <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P23" t="n">
-        <v>90.27585375253976</v>
+        <v>83.66382700900338</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.155140000000017</v>
@@ -2140,10 +2140,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S23" t="n">
-        <v>66.31650407706515</v>
+        <v>62.8792305695363</v>
       </c>
       <c r="T23" t="n">
-        <v>66.31650407706515</v>
+        <v>62.8792305695363</v>
       </c>
     </row>
     <row r="24">
@@ -2204,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P24" t="n">
-        <v>112.6147722017748</v>
+        <v>108.4374685183958</v>
       </c>
       <c r="Q24" t="n">
         <v>1.867959999999982</v>
@@ -2216,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>86.67279796992673</v>
+        <v>84.76145800845967</v>
       </c>
       <c r="T24" t="n">
-        <v>86.67279796992673</v>
+        <v>84.76145800845967</v>
       </c>
     </row>
     <row r="25">
@@ -2278,10 +2278,10 @@
         <v>1.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P25" t="n">
-        <v>108.4314423589757</v>
+        <v>104.2644324555788</v>
       </c>
       <c r="Q25" t="n">
         <v>1.867959999999982</v>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>83.76565309156993</v>
+        <v>81.88330604417715</v>
       </c>
       <c r="T25" t="n">
-        <v>83.76565309156993</v>
+        <v>81.88330604417715</v>
       </c>
     </row>
     <row r="26">
@@ -2352,10 +2352,10 @@
         <v>1.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P26" t="n">
-        <v>108.152553702789</v>
+        <v>103.986230051391</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.438970000000012</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>81.27374001448061</v>
+        <v>79.41063250002367</v>
       </c>
       <c r="T26" t="n">
-        <v>81.27374001448061</v>
+        <v>79.41063250002367</v>
       </c>
     </row>
     <row r="27">
@@ -2426,10 +2426,10 @@
         <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P27" t="n">
-        <v>101.1803372981239</v>
+        <v>97.031169946696</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.438970000000012</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>76.42849855055262</v>
+        <v>74.61371255955279</v>
       </c>
       <c r="T27" t="n">
-        <v>76.42849855055262</v>
+        <v>74.61371255955279</v>
       </c>
     </row>
     <row r="28">
@@ -2500,10 +2500,10 @@
         <v>4.199999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P28" t="n">
-        <v>100.9014486419373</v>
+        <v>96.7529675425082</v>
       </c>
       <c r="Q28" t="n">
         <v>1.867959999999982</v>
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>78.5327923105277</v>
+        <v>76.70263250846861</v>
       </c>
       <c r="T28" t="n">
-        <v>78.5327923105277</v>
+        <v>76.70263250846861</v>
       </c>
     </row>
     <row r="29">
@@ -2574,10 +2574,10 @@
         <v>5.949999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P29" t="n">
-        <v>96.02089715867162</v>
+        <v>91.88442546922168</v>
       </c>
       <c r="Q29" t="n">
         <v>-2.541280000000015</v>
@@ -2586,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>72.07698539440183</v>
+        <v>70.30372622142613</v>
       </c>
       <c r="T29" t="n">
-        <v>72.07698539440183</v>
+        <v>70.30372622142613</v>
       </c>
     </row>
     <row r="30">
@@ -2648,10 +2648,10 @@
         <v>7.199999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P30" t="n">
-        <v>92.53478895633903</v>
+        <v>88.40689541687416</v>
       </c>
       <c r="Q30" t="n">
         <v>-1.438970000000012</v>
@@ -2660,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>70.42039913528191</v>
+        <v>68.6655318333689</v>
       </c>
       <c r="T30" t="n">
-        <v>70.42039913528191</v>
+        <v>68.6655318333689</v>
       </c>
     </row>
     <row r="31">
@@ -2722,10 +2722,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P31" t="n">
-        <v>86.95701583260687</v>
+        <v>82.84284733311816</v>
       </c>
       <c r="Q31" t="n">
         <v>1.867959999999982</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>68.84230938267171</v>
+        <v>67.10879262752687</v>
       </c>
       <c r="T31" t="n">
-        <v>68.84230938267171</v>
+        <v>67.10879262752687</v>
       </c>
     </row>
     <row r="32">
@@ -2796,10 +2796,10 @@
         <v>13.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P32" t="n">
-        <v>74.40702630420952</v>
+        <v>70.32373914466712</v>
       </c>
       <c r="Q32" t="n">
         <v>-1.438970000000012</v>
@@ -2808,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>57.82277132906911</v>
+        <v>56.19353998814465</v>
       </c>
       <c r="T32" t="n">
-        <v>57.82277132906911</v>
+        <v>56.19353998814465</v>
       </c>
     </row>
     <row r="33">
@@ -2872,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P33" t="n">
-        <v>69.93768067962159</v>
+        <v>65.64119475038981</v>
       </c>
       <c r="Q33" t="n">
         <v>-0.3366600000000091</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>55.48289837161757</v>
+        <v>53.72424461198031</v>
       </c>
       <c r="T33" t="n">
-        <v>55.48289837161757</v>
+        <v>53.72424461198031</v>
       </c>
     </row>
     <row r="34">
@@ -2946,10 +2946,10 @@
         <v>1.5</v>
       </c>
       <c r="O34" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P34" t="n">
-        <v>67.14595314102587</v>
+        <v>62.8554640561909</v>
       </c>
       <c r="Q34" t="n">
         <v>-2.541280000000015</v>
@@ -2958,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>52.0107585444601</v>
+        <v>50.28238898534298</v>
       </c>
       <c r="T34" t="n">
-        <v>52.0107585444601</v>
+        <v>50.28238898534298</v>
       </c>
     </row>
     <row r="35">
@@ -3020,10 +3020,10 @@
         <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P35" t="n">
-        <v>66.21537729482729</v>
+        <v>61.9268871581246</v>
       </c>
       <c r="Q35" t="n">
         <v>-2.541280000000015</v>
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>51.364068250637</v>
+        <v>49.64194749791601</v>
       </c>
       <c r="T35" t="n">
-        <v>51.364068250637</v>
+        <v>49.64194749791601</v>
       </c>
     </row>
     <row r="36">
@@ -3094,10 +3094,10 @@
         <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P36" t="n">
-        <v>64.81951352552943</v>
+        <v>60.53402181102515</v>
       </c>
       <c r="Q36" t="n">
         <v>-2.541280000000015</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>50.39403280990233</v>
+        <v>48.68128526677556</v>
       </c>
       <c r="T36" t="n">
-        <v>50.39403280990233</v>
+        <v>48.68128526677556</v>
       </c>
     </row>
     <row r="37">
@@ -3168,10 +3168,10 @@
         <v>2.85</v>
       </c>
       <c r="O37" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P37" t="n">
-        <v>64.63339835628972</v>
+        <v>60.34830643141188</v>
       </c>
       <c r="Q37" t="n">
         <v>-1.438970000000012</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>51.03072922398179</v>
+        <v>49.31346255146838</v>
       </c>
       <c r="T37" t="n">
-        <v>51.03072922398179</v>
+        <v>49.31346255146838</v>
       </c>
     </row>
     <row r="38">
@@ -3242,10 +3242,10 @@
         <v>3.6</v>
       </c>
       <c r="O38" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P38" t="n">
-        <v>63.23753458699186</v>
+        <v>58.95544108431243</v>
       </c>
       <c r="Q38" t="n">
         <v>-0.3366600000000091</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>50.8267282560912</v>
+        <v>49.11306590250615</v>
       </c>
       <c r="T38" t="n">
-        <v>50.8267282560912</v>
+        <v>49.11306590250615</v>
       </c>
     </row>
     <row r="39">
@@ -3316,10 +3316,10 @@
         <v>4.35</v>
       </c>
       <c r="O39" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P39" t="n">
-        <v>61.84167081769399</v>
+        <v>57.56257573721297</v>
       </c>
       <c r="Q39" t="n">
         <v>-2.541280000000015</v>
@@ -3328,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>48.3246238696684</v>
+        <v>46.63187250700926</v>
       </c>
       <c r="T39" t="n">
-        <v>48.3246238696684</v>
+        <v>46.63187250700926</v>
       </c>
     </row>
     <row r="40">
@@ -3390,10 +3390,10 @@
         <v>4.85</v>
       </c>
       <c r="O40" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P40" t="n">
-        <v>60.91109497149542</v>
+        <v>56.63399883914667</v>
       </c>
       <c r="Q40" t="n">
         <v>-1.438970000000012</v>
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>48.44396804868936</v>
+        <v>46.75169660176051</v>
       </c>
       <c r="T40" t="n">
-        <v>48.44396804868936</v>
+        <v>46.75169660176051</v>
       </c>
     </row>
     <row r="41">
@@ -3464,10 +3464,10 @@
         <v>12.35</v>
       </c>
       <c r="O41" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P41" t="n">
-        <v>46.9524572785168</v>
+        <v>42.70534536815212</v>
       </c>
       <c r="Q41" t="n">
         <v>-2.541280000000015</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>37.97757916849869</v>
+        <v>36.38480870817777</v>
       </c>
       <c r="T41" t="n">
-        <v>37.97757916849869</v>
+        <v>36.38480870817777</v>
       </c>
     </row>
     <row r="42">
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P42" t="n">
-        <v>143.3789182823823</v>
+        <v>138.0503353219875</v>
       </c>
       <c r="Q42" t="n">
         <v>-3.643590000000017</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>104.2217262446882</v>
+        <v>101.3841881396789</v>
       </c>
       <c r="T42" t="n">
-        <v>104.2217262446882</v>
+        <v>101.3841881396789</v>
       </c>
     </row>
     <row r="43">
@@ -3614,10 +3614,10 @@
         <v>0.15</v>
       </c>
       <c r="O43" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P43" t="n">
-        <v>143.0450400015963</v>
+        <v>137.7171390037834</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>104.7557368106314</v>
+        <v>101.9146475032443</v>
       </c>
       <c r="T43" t="n">
-        <v>104.7557368106314</v>
+        <v>101.9146475032443</v>
       </c>
     </row>
     <row r="44">
@@ -3688,10 +3688,10 @@
         <v>0.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P44" t="n">
-        <v>142.8224544810724</v>
+        <v>137.4950081249806</v>
       </c>
       <c r="Q44" t="n">
         <v>-2.541280000000015</v>
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>104.6010542060308</v>
+        <v>101.7614433575024</v>
       </c>
       <c r="T44" t="n">
-        <v>104.6010542060308</v>
+        <v>101.7614433575024</v>
       </c>
     </row>
     <row r="45">
@@ -3762,10 +3762,10 @@
         <v>2.25</v>
       </c>
       <c r="O45" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P45" t="n">
-        <v>138.3707440705931</v>
+        <v>133.0523905489256</v>
       </c>
       <c r="Q45" t="n">
         <v>-2.541280000000015</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>101.5074021140186</v>
+        <v>98.69736044266477</v>
       </c>
       <c r="T45" t="n">
-        <v>101.5074021140186</v>
+        <v>98.69736044266477</v>
       </c>
     </row>
     <row r="46">
@@ -3836,10 +3836,10 @@
         <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P46" t="n">
-        <v>137.8142802692832</v>
+        <v>132.4970633519187</v>
       </c>
       <c r="Q46" t="n">
         <v>-2.541280000000015</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>101.1206956025171</v>
+        <v>98.31435007831007</v>
       </c>
       <c r="T46" t="n">
-        <v>101.1206956025171</v>
+        <v>98.31435007831007</v>
       </c>
     </row>
     <row r="47">
@@ -3910,10 +3910,10 @@
         <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P47" t="n">
-        <v>135.5884250640435</v>
+        <v>130.2757545638911</v>
       </c>
       <c r="Q47" t="n">
         <v>4.072579999999988</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>104.1700763935754</v>
+        <v>101.3439021139605</v>
       </c>
       <c r="T47" t="n">
-        <v>104.1700763935754</v>
+        <v>101.3439021139605</v>
       </c>
     </row>
     <row r="48">
@@ -3984,10 +3984,10 @@
         <v>4.25</v>
       </c>
       <c r="O48" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P48" t="n">
-        <v>133.9190336601138</v>
+        <v>128.6097729728705</v>
       </c>
       <c r="Q48" t="n">
         <v>-2.541280000000015</v>
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>98.4137500220064</v>
+        <v>95.63327752782712</v>
       </c>
       <c r="T48" t="n">
-        <v>98.4137500220064</v>
+        <v>95.63327752782712</v>
       </c>
     </row>
     <row r="49">
@@ -4058,10 +4058,10 @@
         <v>4.28</v>
       </c>
       <c r="O49" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P49" t="n">
-        <v>133.8522580039566</v>
+        <v>128.5431337092297</v>
       </c>
       <c r="Q49" t="n">
         <v>-3.643590000000017</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>97.60131076778215</v>
+        <v>94.82705070192634</v>
       </c>
       <c r="T49" t="n">
-        <v>97.60131076778215</v>
+        <v>94.82705070192634</v>
       </c>
     </row>
     <row r="50">
@@ -4132,10 +4132,10 @@
         <v>5.78</v>
       </c>
       <c r="O50" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P50" t="n">
-        <v>130.5134751960971</v>
+        <v>125.2111705271883</v>
       </c>
       <c r="Q50" t="n">
         <v>-2.541280000000015</v>
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>96.04710617161709</v>
+        <v>93.28925409797631</v>
       </c>
       <c r="T50" t="n">
-        <v>96.04710617161709</v>
+        <v>93.28925409797631</v>
       </c>
     </row>
     <row r="51">
@@ -4206,10 +4206,10 @@
         <v>8.780000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P51" t="n">
-        <v>123.8359095803782</v>
+        <v>118.5472441631057</v>
       </c>
       <c r="Q51" t="n">
         <v>-0.3366600000000091</v>
@@ -4218,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>92.93869697928695</v>
+        <v>90.21366089007628</v>
       </c>
       <c r="T51" t="n">
-        <v>92.93869697928695</v>
+        <v>90.21366089007628</v>
       </c>
     </row>
     <row r="52">
@@ -4280,10 +4280,10 @@
         <v>11.28</v>
       </c>
       <c r="O52" t="n">
-        <v>0.2609455566408595</v>
+        <v>0.1699213941233767</v>
       </c>
       <c r="P52" t="n">
-        <v>118.2712715672791</v>
+        <v>112.9939721930369</v>
       </c>
       <c r="Q52" t="n">
         <v>1.867959999999982</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>90.60370080995983</v>
+        <v>87.90408841088563</v>
       </c>
       <c r="T52" t="n">
-        <v>90.60370080995983</v>
+        <v>87.90408841088563</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_ratings/ratings_2026-03-17.xlsx
+++ b/output/daily_ratings/ratings_2026-03-17.xlsx
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P2" t="n">
-        <v>122.6866853493338</v>
+        <v>122.1748841236294</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.438970000000012</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>92.30837681340935</v>
+        <v>92.36163845430819</v>
       </c>
       <c r="T2" t="n">
-        <v>92.30837681340935</v>
+        <v>92.36163845430819</v>
       </c>
     </row>
     <row r="3">
@@ -650,10 +650,10 @@
         <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P3" t="n">
-        <v>116.5620214842595</v>
+        <v>116.0465805764323</v>
       </c>
       <c r="Q3" t="n">
         <v>7.379509999999982</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>94.16630760610863</v>
+        <v>94.27736751831996</v>
       </c>
       <c r="T3" t="n">
-        <v>94.16630760610863</v>
+        <v>94.27736751831996</v>
       </c>
     </row>
     <row r="4">
@@ -724,10 +724,10 @@
         <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P4" t="n">
-        <v>116.0370502958245</v>
+        <v>115.521297415244</v>
       </c>
       <c r="Q4" t="n">
         <v>6.277199999999993</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>93.04396826409675</v>
+        <v>93.11832550825908</v>
       </c>
       <c r="T4" t="n">
-        <v>93.04396826409675</v>
+        <v>93.11832550825908</v>
       </c>
     </row>
     <row r="5">
@@ -798,10 +798,10 @@
         <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P5" t="n">
-        <v>114.2871463343747</v>
+        <v>113.7703535446163</v>
       </c>
       <c r="Q5" t="n">
         <v>4.072579999999988</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>90.31652456696133</v>
+        <v>90.30148847007118</v>
       </c>
       <c r="T5" t="n">
-        <v>90.31652456696133</v>
+        <v>90.30148847007118</v>
       </c>
     </row>
     <row r="6">
@@ -872,10 +872,10 @@
         <v>3.65</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P6" t="n">
-        <v>109.9123864307502</v>
+        <v>109.392993868047</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>81.97738415976636</v>
+        <v>81.68944138157882</v>
       </c>
       <c r="T6" t="n">
-        <v>81.97738415976636</v>
+        <v>81.68944138157882</v>
       </c>
     </row>
     <row r="7">
@@ -946,10 +946,10 @@
         <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P7" t="n">
-        <v>107.2875304885755</v>
+        <v>106.7665780621054</v>
       </c>
       <c r="Q7" t="n">
         <v>5.174889999999976</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>86.24914001802358</v>
+        <v>86.09893553592121</v>
       </c>
       <c r="T7" t="n">
-        <v>86.24914001802358</v>
+        <v>86.09893553592121</v>
       </c>
     </row>
     <row r="8">
@@ -1020,10 +1020,10 @@
         <v>4.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P8" t="n">
-        <v>105.5376265271257</v>
+        <v>105.0156341914777</v>
       </c>
       <c r="Q8" t="n">
         <v>1.867959999999982</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>82.76143073870998</v>
+        <v>82.49712125122201</v>
       </c>
       <c r="T8" t="n">
-        <v>82.76143073870998</v>
+        <v>82.49712125122201</v>
       </c>
     </row>
     <row r="9">
@@ -1094,10 +1094,10 @@
         <v>5.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P9" t="n">
-        <v>102.0378186042261</v>
+        <v>101.5137464502223</v>
       </c>
       <c r="Q9" t="n">
         <v>-6.950520000000012</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>74.26548101572627</v>
+        <v>73.72353818880103</v>
       </c>
       <c r="T9" t="n">
-        <v>74.26548101572627</v>
+        <v>73.72353818880103</v>
       </c>
     </row>
     <row r="10">
@@ -1168,10 +1168,10 @@
         <v>6.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P10" t="n">
-        <v>101.1628666235012</v>
+        <v>100.6382745149084</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.541280000000015</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>76.70308707804963</v>
+        <v>76.24000590226355</v>
       </c>
       <c r="T10" t="n">
-        <v>76.70308707804963</v>
+        <v>76.24000590226355</v>
       </c>
     </row>
     <row r="11">
@@ -1242,10 +1242,10 @@
         <v>6.300000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P11" t="n">
-        <v>100.6378954350663</v>
+        <v>100.1129913537201</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.745900000000006</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>74.82048215385953</v>
+        <v>74.29598664569137</v>
       </c>
       <c r="T11" t="n">
-        <v>74.82048215385953</v>
+        <v>74.29598664569137</v>
       </c>
     </row>
     <row r="12">
@@ -1316,10 +1316,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P12" t="n">
-        <v>90.13847166636748</v>
+        <v>89.6073281299538</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.438970000000012</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>69.85980370372027</v>
+        <v>69.16962311423337</v>
       </c>
       <c r="T12" t="n">
-        <v>69.85980370372027</v>
+        <v>69.16962311423337</v>
       </c>
     </row>
     <row r="13">
@@ -1390,10 +1390,10 @@
         <v>9.550000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P13" t="n">
-        <v>89.26351968564259</v>
+        <v>88.73185619463993</v>
       </c>
       <c r="Q13" t="n">
         <v>2.970269999999999</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>72.29740976604367</v>
+        <v>71.68609082769591</v>
       </c>
       <c r="T13" t="n">
-        <v>72.29740976604367</v>
+        <v>71.68609082769591</v>
       </c>
     </row>
     <row r="14">
@@ -1464,10 +1464,10 @@
         <v>12.55</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P14" t="n">
-        <v>78.76409591694377</v>
+        <v>78.22619297087363</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.541280000000015</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>61.25460665847866</v>
+        <v>60.27990932414755</v>
       </c>
       <c r="T14" t="n">
-        <v>61.25460665847866</v>
+        <v>60.27990932414755</v>
       </c>
     </row>
     <row r="15">
@@ -1538,10 +1538,10 @@
         <v>13.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P15" t="n">
-        <v>74.38933601331928</v>
+        <v>73.84883329430434</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>58.23732532653122</v>
+        <v>57.16270296123428</v>
       </c>
       <c r="T15" t="n">
-        <v>58.23732532653122</v>
+        <v>57.16270296123428</v>
       </c>
     </row>
     <row r="16">
@@ -1612,10 +1612,10 @@
         <v>20.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P16" t="n">
-        <v>53.66937268787446</v>
+        <v>53.18700356556251</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.643590000000017</v>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P17" t="n">
-        <v>96.26313553144195</v>
+        <v>95.73563167715096</v>
       </c>
       <c r="Q17" t="n">
         <v>0.7656499999999937</v>
@@ -1696,10 +1696,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S17" t="n">
-        <v>78.41139104514895</v>
+        <v>78.00176305019129</v>
       </c>
       <c r="T17" t="n">
-        <v>78.41139104514895</v>
+        <v>78.00176305019129</v>
       </c>
     </row>
     <row r="18">
@@ -1758,10 +1758,10 @@
         <v>0.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P18" t="n">
-        <v>95.738164343007</v>
+        <v>95.21034851596265</v>
       </c>
       <c r="Q18" t="n">
         <v>4.072579999999988</v>
@@ -1770,10 +1770,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S18" t="n">
-        <v>80.33011403184989</v>
+        <v>79.98263002617557</v>
       </c>
       <c r="T18" t="n">
-        <v>80.33011403184989</v>
+        <v>79.98263002617557</v>
       </c>
     </row>
     <row r="19">
@@ -1832,10 +1832,10 @@
         <v>0.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P19" t="n">
-        <v>95.56317394686202</v>
+        <v>95.03525412889988</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.438970000000012</v>
@@ -1844,10 +1844,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S19" t="n">
-        <v>76.40809486768089</v>
+        <v>75.93305553910257</v>
       </c>
       <c r="T19" t="n">
-        <v>76.40809486768089</v>
+        <v>75.93305553910257</v>
       </c>
     </row>
     <row r="20">
@@ -1906,10 +1906,10 @@
         <v>1.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P20" t="n">
-        <v>91.18841404323753</v>
+        <v>90.65789445233058</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.541280000000015</v>
@@ -1918,10 +1918,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S20" t="n">
-        <v>72.63054795355524</v>
+        <v>72.03087192967799</v>
       </c>
       <c r="T20" t="n">
-        <v>72.63054795355524</v>
+        <v>72.03087192967799</v>
       </c>
     </row>
     <row r="21">
@@ -1980,10 +1980,10 @@
         <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P21" t="n">
-        <v>86.81365413961302</v>
+        <v>86.28053477576128</v>
       </c>
       <c r="Q21" t="n">
         <v>4.072579999999988</v>
@@ -1992,10 +1992,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S21" t="n">
-        <v>74.17486011467707</v>
+        <v>73.62352904583248</v>
       </c>
       <c r="T21" t="n">
-        <v>74.17486011467707</v>
+        <v>73.62352904583248</v>
       </c>
     </row>
     <row r="22">
@@ -2054,10 +2054,10 @@
         <v>2.85</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P22" t="n">
-        <v>86.28868295117807</v>
+        <v>85.75525161457297</v>
       </c>
       <c r="Q22" t="n">
         <v>-9.155140000000017</v>
@@ -2066,10 +2066,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S22" t="n">
-        <v>64.68959936870476</v>
+        <v>63.82973732414734</v>
       </c>
       <c r="T22" t="n">
-        <v>64.68959936870476</v>
+        <v>63.82973732414734</v>
       </c>
     </row>
     <row r="23">
@@ -2128,10 +2128,10 @@
         <v>3.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P23" t="n">
-        <v>83.66382700900338</v>
+        <v>83.12883580863139</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.155140000000017</v>
@@ -2140,10 +2140,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S23" t="n">
-        <v>62.8792305695363</v>
+        <v>61.95941350639938</v>
       </c>
       <c r="T23" t="n">
-        <v>62.8792305695363</v>
+        <v>61.95941350639938</v>
       </c>
     </row>
     <row r="24">
@@ -2204,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P24" t="n">
-        <v>108.4374685183958</v>
+        <v>108.9168512563342</v>
       </c>
       <c r="Q24" t="n">
         <v>1.867959999999982</v>
@@ -2216,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>84.76145800845967</v>
+        <v>85.27525682979237</v>
       </c>
       <c r="T24" t="n">
-        <v>84.76145800845967</v>
+        <v>85.27525682979237</v>
       </c>
     </row>
     <row r="25">
@@ -2278,10 +2278,10 @@
         <v>1.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P25" t="n">
-        <v>104.2644324555788</v>
+        <v>104.7473088716557</v>
       </c>
       <c r="Q25" t="n">
         <v>1.867959999999982</v>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>81.88330604417715</v>
+        <v>82.30604136378281</v>
       </c>
       <c r="T25" t="n">
-        <v>81.88330604417715</v>
+        <v>82.30604136378281</v>
       </c>
     </row>
     <row r="26">
@@ -2352,10 +2352,10 @@
         <v>1.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P26" t="n">
-        <v>103.986230051391</v>
+        <v>104.4693393793439</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.438970000000012</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>79.41063250002367</v>
+        <v>79.75316192651495</v>
       </c>
       <c r="T26" t="n">
-        <v>79.41063250002367</v>
+        <v>79.75316192651495</v>
       </c>
     </row>
     <row r="27">
@@ -2426,10 +2426,10 @@
         <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P27" t="n">
-        <v>97.031169946696</v>
+        <v>97.5201020715465</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.438970000000012</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>74.61371255955279</v>
+        <v>74.80446948316569</v>
       </c>
       <c r="T27" t="n">
-        <v>74.61371255955279</v>
+        <v>74.80446948316569</v>
       </c>
     </row>
     <row r="28">
@@ -2500,10 +2500,10 @@
         <v>4.199999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P28" t="n">
-        <v>96.7529675425082</v>
+        <v>97.24213257923461</v>
       </c>
       <c r="Q28" t="n">
         <v>1.867959999999982</v>
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>76.70263250846861</v>
+        <v>76.96145352496559</v>
       </c>
       <c r="T28" t="n">
-        <v>76.70263250846861</v>
+        <v>76.96145352496559</v>
       </c>
     </row>
     <row r="29">
@@ -2574,10 +2574,10 @@
         <v>5.949999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P29" t="n">
-        <v>91.88442546922168</v>
+        <v>92.37766646377646</v>
       </c>
       <c r="Q29" t="n">
         <v>-2.541280000000015</v>
@@ -2586,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>70.30372622142613</v>
+        <v>70.35745982857593</v>
       </c>
       <c r="T29" t="n">
-        <v>70.30372622142613</v>
+        <v>70.35745982857593</v>
       </c>
     </row>
     <row r="30">
@@ -2648,10 +2648,10 @@
         <v>7.199999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P30" t="n">
-        <v>88.40689541687416</v>
+        <v>88.90304780987779</v>
       </c>
       <c r="Q30" t="n">
         <v>-1.438970000000012</v>
@@ -2660,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>68.6655318333689</v>
+        <v>68.66809085341261</v>
       </c>
       <c r="T30" t="n">
-        <v>68.6655318333689</v>
+        <v>68.66809085341261</v>
       </c>
     </row>
     <row r="31">
@@ -2722,10 +2722,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P31" t="n">
-        <v>82.84284733311816</v>
+        <v>83.34365796363991</v>
       </c>
       <c r="Q31" t="n">
         <v>1.867959999999982</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>67.10879262752687</v>
+        <v>67.06406863826707</v>
       </c>
       <c r="T31" t="n">
-        <v>67.10879262752687</v>
+        <v>67.06406863826707</v>
       </c>
     </row>
     <row r="32">
@@ -2796,10 +2796,10 @@
         <v>13.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P32" t="n">
-        <v>70.32373914466712</v>
+        <v>70.83503080960469</v>
       </c>
       <c r="Q32" t="n">
         <v>-1.438970000000012</v>
@@ -2808,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>56.19353998814465</v>
+        <v>55.80149050070452</v>
       </c>
       <c r="T32" t="n">
-        <v>56.19353998814465</v>
+        <v>55.80149050070452</v>
       </c>
     </row>
     <row r="33">
@@ -2872,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P33" t="n">
-        <v>65.64119475038981</v>
+        <v>66.03820865674767</v>
       </c>
       <c r="Q33" t="n">
         <v>-0.3366600000000091</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>53.72424461198031</v>
+        <v>53.17055367081799</v>
       </c>
       <c r="T33" t="n">
-        <v>53.72424461198031</v>
+        <v>53.17055367081799</v>
       </c>
     </row>
     <row r="34">
@@ -2946,10 +2946,10 @@
         <v>1.5</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P34" t="n">
-        <v>62.8554640561909</v>
+        <v>63.25453050857856</v>
       </c>
       <c r="Q34" t="n">
         <v>-2.541280000000015</v>
@@ -2958,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>50.28238898534298</v>
+        <v>49.61828566533207</v>
       </c>
       <c r="T34" t="n">
-        <v>50.28238898534298</v>
+        <v>49.61828566533207</v>
       </c>
     </row>
     <row r="35">
@@ -3020,10 +3020,10 @@
         <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P35" t="n">
-        <v>61.9268871581246</v>
+        <v>62.32663779252219</v>
       </c>
       <c r="Q35" t="n">
         <v>-2.541280000000015</v>
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>49.64194749791601</v>
+        <v>48.95751449451096</v>
       </c>
       <c r="T35" t="n">
-        <v>49.64194749791601</v>
+        <v>48.95751449451096</v>
       </c>
     </row>
     <row r="36">
@@ -3094,10 +3094,10 @@
         <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P36" t="n">
-        <v>60.53402181102515</v>
+        <v>60.93479871843763</v>
       </c>
       <c r="Q36" t="n">
         <v>-2.541280000000015</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>48.68128526677556</v>
+        <v>47.96635773827929</v>
       </c>
       <c r="T36" t="n">
-        <v>48.68128526677556</v>
+        <v>47.96635773827929</v>
       </c>
     </row>
     <row r="37">
@@ -3168,10 +3168,10 @@
         <v>2.85</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P37" t="n">
-        <v>60.34830643141188</v>
+        <v>60.74922017522636</v>
       </c>
       <c r="Q37" t="n">
         <v>-1.438970000000012</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>49.31346255146838</v>
+        <v>48.61918075062637</v>
       </c>
       <c r="T37" t="n">
-        <v>49.31346255146838</v>
+        <v>48.61918075062637</v>
       </c>
     </row>
     <row r="38">
@@ -3242,10 +3242,10 @@
         <v>3.6</v>
       </c>
       <c r="O38" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P38" t="n">
-        <v>58.95544108431243</v>
+        <v>59.3573811011418</v>
       </c>
       <c r="Q38" t="n">
         <v>-0.3366600000000091</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>49.11306590250615</v>
+        <v>48.41300124090601</v>
       </c>
       <c r="T38" t="n">
-        <v>49.11306590250615</v>
+        <v>48.41300124090601</v>
       </c>
     </row>
     <row r="39">
@@ -3316,10 +3316,10 @@
         <v>4.35</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P39" t="n">
-        <v>57.56257573721297</v>
+        <v>57.96554202705725</v>
       </c>
       <c r="Q39" t="n">
         <v>-2.541280000000015</v>
@@ -3328,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>46.63187250700926</v>
+        <v>45.85188999165175</v>
       </c>
       <c r="T39" t="n">
-        <v>46.63187250700926</v>
+        <v>45.85188999165175</v>
       </c>
     </row>
     <row r="40">
@@ -3390,10 +3390,10 @@
         <v>4.85</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P40" t="n">
-        <v>56.63399883914667</v>
+        <v>57.03764931100088</v>
       </c>
       <c r="Q40" t="n">
         <v>-1.438970000000012</v>
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>46.75169660176051</v>
+        <v>45.97609606734193</v>
       </c>
       <c r="T40" t="n">
-        <v>46.75169660176051</v>
+        <v>45.97609606734193</v>
       </c>
     </row>
     <row r="41">
@@ -3464,10 +3464,10 @@
         <v>12.35</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P41" t="n">
-        <v>42.70534536815212</v>
+        <v>43.11925857015532</v>
       </c>
       <c r="Q41" t="n">
         <v>-2.541280000000015</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>36.38480870817777</v>
+        <v>35.279551258514</v>
       </c>
       <c r="T41" t="n">
-        <v>36.38480870817777</v>
+        <v>35.279551258514</v>
       </c>
     </row>
     <row r="42">
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P42" t="n">
-        <v>138.0503353219875</v>
+        <v>137.2226240526732</v>
       </c>
       <c r="Q42" t="n">
         <v>-3.643590000000017</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>101.3841881396789</v>
+        <v>101.5074839229288</v>
       </c>
       <c r="T42" t="n">
-        <v>101.3841881396789</v>
+        <v>101.5074839229288</v>
       </c>
     </row>
     <row r="43">
@@ -3614,10 +3614,10 @@
         <v>0.15</v>
       </c>
       <c r="O43" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P43" t="n">
-        <v>137.7171390037834</v>
+        <v>136.8892761093649</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>101.9146475032443</v>
+        <v>102.0550773566576</v>
       </c>
       <c r="T43" t="n">
-        <v>101.9146475032443</v>
+        <v>102.0550773566576</v>
       </c>
     </row>
     <row r="44">
@@ -3688,10 +3688,10 @@
         <v>0.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P44" t="n">
-        <v>137.4950081249806</v>
+        <v>136.6670441471594</v>
       </c>
       <c r="Q44" t="n">
         <v>-2.541280000000015</v>
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>101.7614433575024</v>
+        <v>101.8968214814692</v>
       </c>
       <c r="T44" t="n">
-        <v>101.7614433575024</v>
+        <v>101.8968214814692</v>
       </c>
     </row>
     <row r="45">
@@ -3762,10 +3762,10 @@
         <v>2.25</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P45" t="n">
-        <v>133.0523905489256</v>
+        <v>132.2224049030491</v>
       </c>
       <c r="Q45" t="n">
         <v>-2.541280000000015</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>98.69736044266477</v>
+        <v>98.73170397770184</v>
       </c>
       <c r="T45" t="n">
-        <v>98.69736044266477</v>
+        <v>98.73170397770184</v>
       </c>
     </row>
     <row r="46">
@@ -3836,10 +3836,10 @@
         <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P46" t="n">
-        <v>132.4970633519187</v>
+        <v>131.6668249975353</v>
       </c>
       <c r="Q46" t="n">
         <v>-2.541280000000015</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>98.31435007831007</v>
+        <v>98.33606428973091</v>
       </c>
       <c r="T46" t="n">
-        <v>98.31435007831007</v>
+        <v>98.33606428973091</v>
       </c>
     </row>
     <row r="47">
@@ -3910,10 +3910,10 @@
         <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P47" t="n">
-        <v>130.2757545638911</v>
+        <v>129.4445053754801</v>
       </c>
       <c r="Q47" t="n">
         <v>4.072579999999988</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>101.3439021139605</v>
+        <v>101.463369016915</v>
       </c>
       <c r="T47" t="n">
-        <v>101.3439021139605</v>
+        <v>101.463369016915</v>
       </c>
     </row>
     <row r="48">
@@ -3984,10 +3984,10 @@
         <v>4.25</v>
       </c>
       <c r="O48" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P48" t="n">
-        <v>128.6097729728705</v>
+        <v>127.7777656589387</v>
       </c>
       <c r="Q48" t="n">
         <v>-2.541280000000015</v>
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>95.63327752782712</v>
+        <v>95.56658647393449</v>
       </c>
       <c r="T48" t="n">
-        <v>95.63327752782712</v>
+        <v>95.56658647393449</v>
       </c>
     </row>
     <row r="49">
@@ -4058,10 +4058,10 @@
         <v>4.28</v>
       </c>
       <c r="O49" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P49" t="n">
-        <v>128.5431337092297</v>
+        <v>127.7110960702771</v>
       </c>
       <c r="Q49" t="n">
         <v>-3.643590000000017</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>94.82705070192634</v>
+        <v>94.73413246486669</v>
       </c>
       <c r="T49" t="n">
-        <v>94.82705070192634</v>
+        <v>94.73413246486669</v>
       </c>
     </row>
     <row r="50">
@@ -4132,10 +4132,10 @@
         <v>5.78</v>
       </c>
       <c r="O50" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P50" t="n">
-        <v>125.2111705271883</v>
+        <v>124.3776166371943</v>
       </c>
       <c r="Q50" t="n">
         <v>-2.541280000000015</v>
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>93.28925409797631</v>
+        <v>93.14527158355249</v>
       </c>
       <c r="T50" t="n">
-        <v>93.28925409797631</v>
+        <v>93.14527158355249</v>
       </c>
     </row>
     <row r="51">
@@ -4206,10 +4206,10 @@
         <v>8.780000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P51" t="n">
-        <v>118.5472441631057</v>
+        <v>117.7106577710288</v>
       </c>
       <c r="Q51" t="n">
         <v>-0.3366600000000091</v>
@@ -4218,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>90.21366089007628</v>
+        <v>89.96754982092405</v>
       </c>
       <c r="T51" t="n">
-        <v>90.21366089007628</v>
+        <v>89.96754982092405</v>
       </c>
     </row>
     <row r="52">
@@ -4280,10 +4280,10 @@
         <v>11.28</v>
       </c>
       <c r="O52" t="n">
-        <v>0.1699213941233767</v>
+        <v>0.1749505941233769</v>
       </c>
       <c r="P52" t="n">
-        <v>112.9939721930369</v>
+        <v>112.1548587158909</v>
       </c>
       <c r="Q52" t="n">
         <v>1.867959999999982</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>87.90408841088563</v>
+        <v>87.58110743423745</v>
       </c>
       <c r="T52" t="n">
-        <v>87.90408841088563</v>
+        <v>87.58110743423745</v>
       </c>
     </row>
   </sheetData>

--- a/output/daily_ratings/ratings_2026-03-17.xlsx
+++ b/output/daily_ratings/ratings_2026-03-17.xlsx
@@ -579,7 +579,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P2" t="n">
-        <v>122.1748841236294</v>
+        <v>122.1748282788496</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.438970000000012</v>
@@ -588,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>92.36163845430819</v>
+        <v>92.53572862886182</v>
       </c>
       <c r="T2" t="n">
-        <v>92.36163845430819</v>
+        <v>92.53572862886182</v>
       </c>
     </row>
     <row r="3">
@@ -653,7 +653,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P3" t="n">
-        <v>116.0465805764323</v>
+        <v>116.0465401650483</v>
       </c>
       <c r="Q3" t="n">
         <v>7.379509999999982</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>94.27736751831996</v>
+        <v>94.45152949847552</v>
       </c>
       <c r="T3" t="n">
-        <v>94.27736751831996</v>
+        <v>94.45152949847552</v>
       </c>
     </row>
     <row r="4">
@@ -727,7 +727,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P4" t="n">
-        <v>115.521297415244</v>
+        <v>115.5212583267225</v>
       </c>
       <c r="Q4" t="n">
         <v>6.277199999999993</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>93.11832550825908</v>
+        <v>93.29245163669268</v>
       </c>
       <c r="T4" t="n">
-        <v>93.11832550825908</v>
+        <v>93.29245163669268</v>
       </c>
     </row>
     <row r="5">
@@ -801,7 +801,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P5" t="n">
-        <v>113.7703535446163</v>
+        <v>113.7703188656364</v>
       </c>
       <c r="Q5" t="n">
         <v>4.072579999999988</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>90.30148847007118</v>
+        <v>90.4755283182355</v>
       </c>
       <c r="T5" t="n">
-        <v>90.30148847007118</v>
+        <v>90.4755283182355</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P6" t="n">
-        <v>109.392993868047</v>
+        <v>109.3929702129212</v>
       </c>
       <c r="Q6" t="n">
         <v>-3.643590000000017</v>
@@ -884,10 +884,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>81.68944138157882</v>
+        <v>81.86321569086405</v>
       </c>
       <c r="T6" t="n">
-        <v>81.68944138157882</v>
+        <v>81.86321569086405</v>
       </c>
     </row>
     <row r="7">
@@ -949,7 +949,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P7" t="n">
-        <v>106.7665780621054</v>
+        <v>106.7665610212921</v>
       </c>
       <c r="Q7" t="n">
         <v>5.174889999999976</v>
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>86.09893553592121</v>
+        <v>86.27285453493508</v>
       </c>
       <c r="T7" t="n">
-        <v>86.09893553592121</v>
+        <v>86.27285453493508</v>
       </c>
     </row>
     <row r="8">
@@ -1023,7 +1023,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P8" t="n">
-        <v>105.0156341914777</v>
+        <v>105.015621560206</v>
       </c>
       <c r="Q8" t="n">
         <v>1.867959999999982</v>
@@ -1032,10 +1032,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>82.49712125122201</v>
+        <v>82.67092905086366</v>
       </c>
       <c r="T8" t="n">
-        <v>82.49712125122201</v>
+        <v>82.67092905086366</v>
       </c>
     </row>
     <row r="9">
@@ -1097,7 +1097,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P9" t="n">
-        <v>101.5137464502223</v>
+        <v>101.5137426380338</v>
       </c>
       <c r="Q9" t="n">
         <v>-6.950520000000012</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>73.72353818880103</v>
+        <v>73.89707375149229</v>
       </c>
       <c r="T9" t="n">
-        <v>73.72353818880103</v>
+        <v>73.89707375149229</v>
       </c>
     </row>
     <row r="10">
@@ -1171,7 +1171,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P10" t="n">
-        <v>100.6382745149084</v>
+        <v>100.6382729074908</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.541280000000015</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>76.24000590226355</v>
+        <v>76.41362292033497</v>
       </c>
       <c r="T10" t="n">
-        <v>76.24000590226355</v>
+        <v>76.41362292033497</v>
       </c>
     </row>
     <row r="11">
@@ -1245,7 +1245,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P11" t="n">
-        <v>100.1129913537201</v>
+        <v>100.112991069165</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.745900000000006</v>
@@ -1254,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>74.29598664569137</v>
+        <v>74.46954289293787</v>
       </c>
       <c r="T11" t="n">
-        <v>74.29598664569137</v>
+        <v>74.46954289293787</v>
       </c>
     </row>
     <row r="12">
@@ -1319,7 +1319,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P12" t="n">
-        <v>89.6073281299538</v>
+        <v>89.60735430264847</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.438970000000012</v>
@@ -1328,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>69.16962311423337</v>
+        <v>69.34303546640864</v>
       </c>
       <c r="T12" t="n">
-        <v>69.16962311423337</v>
+        <v>69.34303546640864</v>
       </c>
     </row>
     <row r="13">
@@ -1393,7 +1393,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P13" t="n">
-        <v>88.73185619463993</v>
+        <v>88.73188457210543</v>
       </c>
       <c r="Q13" t="n">
         <v>2.970269999999999</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>71.68609082769591</v>
+        <v>71.85958463525132</v>
       </c>
       <c r="T13" t="n">
-        <v>71.68609082769591</v>
+        <v>71.85958463525132</v>
       </c>
     </row>
     <row r="14">
@@ -1467,7 +1467,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P14" t="n">
-        <v>78.22619297087363</v>
+        <v>78.22624780558894</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.541280000000015</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>60.27990932414755</v>
+        <v>60.45305988380806</v>
       </c>
       <c r="T14" t="n">
-        <v>60.27990932414755</v>
+        <v>60.45305988380806</v>
       </c>
     </row>
     <row r="15">
@@ -1541,7 +1541,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P15" t="n">
-        <v>73.84883329430434</v>
+        <v>73.84889915287373</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.541280000000015</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>57.16270296123428</v>
+        <v>57.33576241573638</v>
       </c>
       <c r="T15" t="n">
-        <v>57.16270296123428</v>
+        <v>57.33576241573638</v>
       </c>
     </row>
     <row r="16">
@@ -1615,7 +1615,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P16" t="n">
-        <v>53.18700356556251</v>
+        <v>53.18712145846605</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.643590000000017</v>
@@ -1687,7 +1687,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P17" t="n">
-        <v>95.73563167715096</v>
+        <v>95.73564241644992</v>
       </c>
       <c r="Q17" t="n">
         <v>0.7656499999999937</v>
@@ -1696,10 +1696,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S17" t="n">
-        <v>78.00176305019129</v>
+        <v>78.17544478786969</v>
       </c>
       <c r="T17" t="n">
-        <v>78.00176305019129</v>
+        <v>78.17544478786969</v>
       </c>
     </row>
     <row r="18">
@@ -1761,7 +1761,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P18" t="n">
-        <v>95.21034851596265</v>
+        <v>95.2103605781241</v>
       </c>
       <c r="Q18" t="n">
         <v>4.072579999999988</v>
@@ -1770,10 +1770,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S18" t="n">
-        <v>79.98263002617557</v>
+        <v>80.15637558854385</v>
       </c>
       <c r="T18" t="n">
-        <v>79.98263002617557</v>
+        <v>80.15637558854385</v>
       </c>
     </row>
     <row r="19">
@@ -1835,7 +1835,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P19" t="n">
-        <v>95.03525412889988</v>
+        <v>95.03526663201549</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.438970000000012</v>
@@ -1844,10 +1844,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S19" t="n">
-        <v>75.93305553910257</v>
+        <v>76.10667286174971</v>
       </c>
       <c r="T19" t="n">
-        <v>75.93305553910257</v>
+        <v>76.10667286174971</v>
       </c>
     </row>
     <row r="20">
@@ -1909,7 +1909,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P20" t="n">
-        <v>90.65789445233058</v>
+        <v>90.65791797930028</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.541280000000015</v>
@@ -1918,10 +1918,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S20" t="n">
-        <v>72.03087192967799</v>
+        <v>72.20437322806379</v>
       </c>
       <c r="T20" t="n">
-        <v>72.03087192967799</v>
+        <v>72.20437322806379</v>
       </c>
     </row>
     <row r="21">
@@ -1983,7 +1983,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P21" t="n">
-        <v>86.28053477576128</v>
+        <v>86.28056932658507</v>
       </c>
       <c r="Q21" t="n">
         <v>4.072579999999988</v>
@@ -1992,10 +1992,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S21" t="n">
-        <v>73.62352904583248</v>
+        <v>73.79708875367766</v>
       </c>
       <c r="T21" t="n">
-        <v>73.62352904583248</v>
+        <v>73.79708875367766</v>
       </c>
     </row>
     <row r="22">
@@ -2057,7 +2057,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P22" t="n">
-        <v>85.75525161457297</v>
+        <v>85.75528748825926</v>
       </c>
       <c r="Q22" t="n">
         <v>-9.155140000000017</v>
@@ -2066,10 +2066,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S22" t="n">
-        <v>63.82973732414734</v>
+        <v>64.00298707013799</v>
       </c>
       <c r="T22" t="n">
-        <v>63.82973732414734</v>
+        <v>64.00298707013799</v>
       </c>
     </row>
     <row r="23">
@@ -2131,7 +2131,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P23" t="n">
-        <v>83.12883580863139</v>
+        <v>83.12887829663012</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.155140000000017</v>
@@ -2140,10 +2140,10 @@
         <v>4.069673109043189</v>
       </c>
       <c r="S23" t="n">
-        <v>61.95941350639938</v>
+        <v>62.132608589295</v>
       </c>
       <c r="T23" t="n">
-        <v>61.95941350639938</v>
+        <v>62.132608589295</v>
       </c>
     </row>
     <row r="24">
@@ -2207,7 +2207,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P24" t="n">
-        <v>108.9168512563342</v>
+        <v>108.9168563878038</v>
       </c>
       <c r="Q24" t="n">
         <v>1.867959999999982</v>
@@ -2216,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>85.27525682979237</v>
+        <v>85.44916547095787</v>
       </c>
       <c r="T24" t="n">
-        <v>85.27525682979237</v>
+        <v>85.44916547095787</v>
       </c>
     </row>
     <row r="25">
@@ -2281,7 +2281,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P25" t="n">
-        <v>104.7473088716557</v>
+        <v>104.7473116036371</v>
       </c>
       <c r="Q25" t="n">
         <v>1.867959999999982</v>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>82.30604136378281</v>
+        <v>82.47985403842392</v>
       </c>
       <c r="T25" t="n">
-        <v>82.30604136378281</v>
+        <v>82.47985403842392</v>
       </c>
     </row>
     <row r="26">
@@ -2355,7 +2355,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P26" t="n">
-        <v>104.4693393793439</v>
+        <v>104.4693419513593</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.438970000000012</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>79.75316192651495</v>
+        <v>79.92689344607889</v>
       </c>
       <c r="T26" t="n">
-        <v>79.75316192651495</v>
+        <v>79.92689344607889</v>
       </c>
     </row>
     <row r="27">
@@ -2429,7 +2429,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P27" t="n">
-        <v>97.5201020715465</v>
+        <v>97.52010064441481</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.438970000000012</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>74.80446948316569</v>
+        <v>74.97804105852234</v>
       </c>
       <c r="T27" t="n">
-        <v>74.80446948316569</v>
+        <v>74.97804105852234</v>
       </c>
     </row>
     <row r="28">
@@ -2503,7 +2503,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P28" t="n">
-        <v>97.24213257923461</v>
+        <v>97.24213099213704</v>
       </c>
       <c r="Q28" t="n">
         <v>1.867959999999982</v>
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>76.96145352496559</v>
+        <v>77.13509345986283</v>
       </c>
       <c r="T28" t="n">
-        <v>76.96145352496559</v>
+        <v>77.13509345986283</v>
       </c>
     </row>
     <row r="29">
@@ -2577,7 +2577,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P29" t="n">
-        <v>92.37766646377646</v>
+        <v>92.37766207727587</v>
       </c>
       <c r="Q29" t="n">
         <v>-2.541280000000015</v>
@@ -2586,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>70.35745982857593</v>
+        <v>70.53088812611621</v>
       </c>
       <c r="T29" t="n">
-        <v>70.35745982857593</v>
+        <v>70.53088812611621</v>
       </c>
     </row>
     <row r="30">
@@ -2651,7 +2651,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P30" t="n">
-        <v>88.90304780987779</v>
+        <v>88.90304142380361</v>
       </c>
       <c r="Q30" t="n">
         <v>-1.438970000000012</v>
@@ -2660,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>68.66809085341261</v>
+        <v>68.8414640979522</v>
       </c>
       <c r="T30" t="n">
-        <v>68.66809085341261</v>
+        <v>68.8414640979522</v>
       </c>
     </row>
     <row r="31">
@@ -2725,7 +2725,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P31" t="n">
-        <v>83.34365796363991</v>
+        <v>83.34364837824799</v>
       </c>
       <c r="Q31" t="n">
         <v>1.867959999999982</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>67.06406863826707</v>
+        <v>67.23738868474969</v>
       </c>
       <c r="T31" t="n">
-        <v>67.06406863826707</v>
+        <v>67.23738868474969</v>
       </c>
     </row>
     <row r="32">
@@ -2799,7 +2799,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P32" t="n">
-        <v>70.83503080960469</v>
+        <v>70.83501402574787</v>
       </c>
       <c r="Q32" t="n">
         <v>-1.438970000000012</v>
@@ -2808,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>55.80149050070452</v>
+        <v>55.97444789030511</v>
       </c>
       <c r="T32" t="n">
-        <v>55.80149050070452</v>
+        <v>55.97444789030511</v>
       </c>
     </row>
     <row r="33">
@@ -2875,7 +2875,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P33" t="n">
-        <v>66.03820865674767</v>
+        <v>66.03804919586062</v>
       </c>
       <c r="Q33" t="n">
         <v>-0.3366600000000091</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>53.17055367081799</v>
+        <v>53.3433259349036</v>
       </c>
       <c r="T33" t="n">
-        <v>53.17055367081799</v>
+        <v>53.3433259349036</v>
       </c>
     </row>
     <row r="34">
@@ -2949,7 +2949,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P34" t="n">
-        <v>63.25453050857856</v>
+        <v>63.25435797748028</v>
       </c>
       <c r="Q34" t="n">
         <v>-2.541280000000015</v>
@@ -2958,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>49.61828566533207</v>
+        <v>49.79093585481137</v>
       </c>
       <c r="T34" t="n">
-        <v>49.61828566533207</v>
+        <v>49.79093585481137</v>
       </c>
     </row>
     <row r="35">
@@ -3023,7 +3023,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P35" t="n">
-        <v>62.32663779252219</v>
+        <v>62.32646090468683</v>
       </c>
       <c r="Q35" t="n">
         <v>-2.541280000000015</v>
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>48.95751449451096</v>
+        <v>49.13014060519014</v>
       </c>
       <c r="T35" t="n">
-        <v>48.95751449451096</v>
+        <v>49.13014060519014</v>
       </c>
     </row>
     <row r="36">
@@ -3097,7 +3097,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P36" t="n">
-        <v>60.93479871843763</v>
+        <v>60.93461529549666</v>
       </c>
       <c r="Q36" t="n">
         <v>-2.541280000000015</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>47.96635773827929</v>
+        <v>48.13894773075828</v>
       </c>
       <c r="T36" t="n">
-        <v>47.96635773827929</v>
+        <v>48.13894773075828</v>
       </c>
     </row>
     <row r="37">
@@ -3171,7 +3171,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P37" t="n">
-        <v>60.74922017522636</v>
+        <v>60.74903588093797</v>
       </c>
       <c r="Q37" t="n">
         <v>-1.438970000000012</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>48.61918075062637</v>
+        <v>48.79179084644829</v>
       </c>
       <c r="T37" t="n">
-        <v>48.61918075062637</v>
+        <v>48.79179084644829</v>
       </c>
     </row>
     <row r="38">
@@ -3245,7 +3245,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P38" t="n">
-        <v>59.3573811011418</v>
+        <v>59.35719027174779</v>
       </c>
       <c r="Q38" t="n">
         <v>-0.3366600000000091</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>48.41300124090601</v>
+        <v>48.58560013763069</v>
       </c>
       <c r="T38" t="n">
-        <v>48.41300124090601</v>
+        <v>48.58560013763069</v>
       </c>
     </row>
     <row r="39">
@@ -3319,7 +3319,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P39" t="n">
-        <v>57.96554202705725</v>
+        <v>57.96534466255762</v>
       </c>
       <c r="Q39" t="n">
         <v>-2.541280000000015</v>
@@ -3328,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>45.85188999165175</v>
+        <v>46.02440293197032</v>
       </c>
       <c r="T39" t="n">
-        <v>45.85188999165175</v>
+        <v>46.02440293197032</v>
       </c>
     </row>
     <row r="40">
@@ -3393,7 +3393,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P40" t="n">
-        <v>57.03764931100088</v>
+        <v>57.03744758976417</v>
       </c>
       <c r="Q40" t="n">
         <v>-1.438970000000012</v>
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>45.97609606734193</v>
+        <v>46.14860984796334</v>
       </c>
       <c r="T40" t="n">
-        <v>45.97609606734193</v>
+        <v>46.14860984796334</v>
       </c>
     </row>
     <row r="41">
@@ -3467,7 +3467,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P41" t="n">
-        <v>43.11925857015532</v>
+        <v>43.11899149786243</v>
       </c>
       <c r="Q41" t="n">
         <v>-2.541280000000015</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>35.279551258514</v>
+        <v>35.45167893803053</v>
       </c>
       <c r="T41" t="n">
-        <v>35.279551258514</v>
+        <v>35.45167893803053</v>
       </c>
     </row>
     <row r="42">
@@ -3543,7 +3543,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P42" t="n">
-        <v>137.2226240526732</v>
+        <v>137.2226413767617</v>
       </c>
       <c r="Q42" t="n">
         <v>-3.643590000000017</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>101.5074839229288</v>
+        <v>101.681916539035</v>
       </c>
       <c r="T42" t="n">
-        <v>101.5074839229288</v>
+        <v>101.681916539035</v>
       </c>
     </row>
     <row r="43">
@@ -3617,7 +3617,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P43" t="n">
-        <v>136.8892761093649</v>
+        <v>136.8892932783072</v>
       </c>
       <c r="Q43" t="n">
         <v>-2.541280000000015</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>102.0550773566576</v>
+        <v>102.2295272456313</v>
       </c>
       <c r="T43" t="n">
-        <v>102.0550773566576</v>
+        <v>102.2295272456313</v>
       </c>
     </row>
     <row r="44">
@@ -3691,7 +3691,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P44" t="n">
-        <v>136.6670441471594</v>
+        <v>136.6670612126709</v>
       </c>
       <c r="Q44" t="n">
         <v>-2.541280000000015</v>
@@ -3700,10 +3700,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>101.8968214814692</v>
+        <v>102.0712662729526</v>
       </c>
       <c r="T44" t="n">
-        <v>101.8968214814692</v>
+        <v>102.0712662729526</v>
       </c>
     </row>
     <row r="45">
@@ -3765,7 +3765,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P45" t="n">
-        <v>132.2224049030491</v>
+        <v>132.2224198999443</v>
       </c>
       <c r="Q45" t="n">
         <v>-2.541280000000015</v>
@@ -3774,10 +3774,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>98.73170397770184</v>
+        <v>98.90604681937877</v>
       </c>
       <c r="T45" t="n">
-        <v>98.73170397770184</v>
+        <v>98.90604681937877</v>
       </c>
     </row>
     <row r="46">
@@ -3839,7 +3839,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P46" t="n">
-        <v>131.6668249975353</v>
+        <v>131.6668397358535</v>
       </c>
       <c r="Q46" t="n">
         <v>-2.541280000000015</v>
@@ -3848,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>98.33606428973091</v>
+        <v>98.51039438768204</v>
       </c>
       <c r="T46" t="n">
-        <v>98.33606428973091</v>
+        <v>98.51039438768204</v>
       </c>
     </row>
     <row r="47">
@@ -3913,7 +3913,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P47" t="n">
-        <v>129.4445053754801</v>
+        <v>129.4445190794902</v>
       </c>
       <c r="Q47" t="n">
         <v>4.072579999999988</v>
@@ -3922,10 +3922,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>101.463369016915</v>
+        <v>101.6377976545807</v>
       </c>
       <c r="T47" t="n">
-        <v>101.463369016915</v>
+        <v>101.6377976545807</v>
       </c>
     </row>
     <row r="48">
@@ -3987,7 +3987,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P48" t="n">
-        <v>127.7777656589387</v>
+        <v>127.7777785872178</v>
       </c>
       <c r="Q48" t="n">
         <v>-2.541280000000015</v>
@@ -3996,10 +3996,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>95.56658647393449</v>
+        <v>95.74082736580499</v>
       </c>
       <c r="T48" t="n">
-        <v>95.56658647393449</v>
+        <v>95.74082736580499</v>
       </c>
     </row>
     <row r="49">
@@ -4061,7 +4061,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P49" t="n">
-        <v>127.7110960702771</v>
+        <v>127.7111089675269</v>
       </c>
       <c r="Q49" t="n">
         <v>-3.643590000000017</v>
@@ -4070,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>94.73413246486669</v>
+        <v>94.90834690838712</v>
       </c>
       <c r="T49" t="n">
-        <v>94.73413246486669</v>
+        <v>94.90834690838712</v>
       </c>
     </row>
     <row r="50">
@@ -4135,7 +4135,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P50" t="n">
-        <v>124.3776166371943</v>
+        <v>124.3776279829819</v>
       </c>
       <c r="Q50" t="n">
         <v>-2.541280000000015</v>
@@ -4144,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>93.14527158355249</v>
+        <v>93.31943448382103</v>
       </c>
       <c r="T50" t="n">
-        <v>93.14527158355249</v>
+        <v>93.31943448382103</v>
       </c>
     </row>
     <row r="51">
@@ -4209,7 +4209,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P51" t="n">
-        <v>117.7106577710288</v>
+        <v>117.7106660138921</v>
       </c>
       <c r="Q51" t="n">
         <v>-0.3366600000000091</v>
@@ -4218,10 +4218,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>89.96754982092405</v>
+        <v>90.14160963468885</v>
       </c>
       <c r="T51" t="n">
-        <v>89.96754982092405</v>
+        <v>90.14160963468885</v>
       </c>
     </row>
     <row r="52">
@@ -4283,7 +4283,7 @@
         <v>0.1749505941233769</v>
       </c>
       <c r="P52" t="n">
-        <v>112.1548587158909</v>
+        <v>112.1548643729839</v>
       </c>
       <c r="Q52" t="n">
         <v>1.867959999999982</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>87.58110743423745</v>
+        <v>87.7550896489501</v>
       </c>
       <c r="T52" t="n">
-        <v>87.58110743423745</v>
+        <v>87.7550896489501</v>
       </c>
     </row>
   </sheetData>
